--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1701,13 +1701,13 @@
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.34</v>
+        <v>2.4</v>
       </c>
       <c r="M10" t="n">
-        <v>3.2</v>
+        <v>3.25</v>
       </c>
       <c r="N10" t="n">
-        <v>2.8</v>
+        <v>2.85</v>
       </c>
       <c r="O10" t="n">
         <v>0</v>
@@ -1740,10 +1740,10 @@
         <v>0</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.08</v>
+        <v>2.05</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.72</v>
+        <v>1.68</v>
       </c>
       <c r="AA10" t="n">
         <v>0</v>
@@ -1830,13 +1830,13 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.81</v>
+        <v>1.75</v>
       </c>
       <c r="M11" t="n">
-        <v>3.3</v>
+        <v>3.45</v>
       </c>
       <c r="N11" t="n">
-        <v>4.1</v>
+        <v>4.5</v>
       </c>
       <c r="O11" t="n">
         <v>0</v>
@@ -1869,10 +1869,10 @@
         <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.3</v>
+        <v>2.1</v>
       </c>
       <c r="Z11" t="n">
-        <v>1.59</v>
+        <v>1.65</v>
       </c>
       <c r="AA11" t="n">
         <v>0</v>
@@ -2217,10 +2217,10 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.15</v>
+        <v>3.2</v>
       </c>
       <c r="M14" t="n">
-        <v>3.15</v>
+        <v>3.25</v>
       </c>
       <c r="N14" t="n">
         <v>2.15</v>
@@ -2256,10 +2256,10 @@
         <v>0</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.23</v>
+        <v>2.12</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.63</v>
+        <v>1.64</v>
       </c>
       <c r="AA14" t="n">
         <v>0</v>

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -886,7 +886,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1006,7 +1006,7 @@
         <v>0</v>
       </c>
       <c r="AK4" s="3" t="n">
-        <v>45939.5</v>
+        <v>45939.54166666666</v>
       </c>
     </row>
     <row r="5">
@@ -1015,7 +1015,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1135,7 +1135,7 @@
         <v>0</v>
       </c>
       <c r="AK5" s="3" t="n">
-        <v>45939.5</v>
+        <v>45939.54166666666</v>
       </c>
     </row>
     <row r="6">
@@ -1144,7 +1144,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1264,7 +1264,7 @@
         <v>0</v>
       </c>
       <c r="AK6" s="3" t="n">
-        <v>45939.5</v>
+        <v>45939.54166666666</v>
       </c>
     </row>
     <row r="7">
@@ -1273,7 +1273,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1393,7 +1393,7 @@
         <v>0</v>
       </c>
       <c r="AK7" s="3" t="n">
-        <v>45939.5</v>
+        <v>45939.54166666666</v>
       </c>
     </row>
     <row r="8">
@@ -1402,7 +1402,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1522,7 +1522,7 @@
         <v>0</v>
       </c>
       <c r="AK8" s="3" t="n">
-        <v>45939.5</v>
+        <v>45939.54166666666</v>
       </c>
     </row>
     <row r="9">
@@ -1531,7 +1531,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1651,7 +1651,7 @@
         <v>0</v>
       </c>
       <c r="AK9" s="3" t="n">
-        <v>45939.5</v>
+        <v>45939.54166666666</v>
       </c>
     </row>
     <row r="10">

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R13" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T13" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="U13" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V13" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X13" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y13" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA13" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1955,65 +1955,65 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="M12" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="N12" t="n">
-        <v>3.65</v>
+        <v>0</v>
       </c>
       <c r="O12" t="n">
-        <v>2.7</v>
+        <v>0</v>
       </c>
       <c r="P12" t="n">
-        <v>1.98</v>
+        <v>0</v>
       </c>
       <c r="Q12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="R12" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="S12" t="n">
-        <v>2.6</v>
+        <v>0</v>
       </c>
       <c r="T12" t="n">
-        <v>3.19</v>
+        <v>0</v>
       </c>
       <c r="U12" t="n">
-        <v>1.32</v>
+        <v>0</v>
       </c>
       <c r="V12" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="X12" t="n">
-        <v>2.88</v>
+        <v>0</v>
       </c>
       <c r="Y12" t="n">
-        <v>2.15</v>
+        <v>0</v>
       </c>
       <c r="Z12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AA12" t="n">
-        <v>3.9</v>
+        <v>0</v>
       </c>
       <c r="AB12" t="n">
-        <v>1.25</v>
+        <v>0</v>
       </c>
       <c r="AC12" t="n">
-        <v>1.85</v>
+        <v>0</v>
       </c>
       <c r="AD12" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,10 +2026,10 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AH12" t="n">
-        <v>1.7</v>
+        <v>0</v>
       </c>
       <c r="AI12" t="n">
         <v>0</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,65 +2084,65 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>suspended</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>3.15</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>3.65</v>
       </c>
       <c r="O13" t="n">
-        <v>0</v>
+        <v>2.7</v>
       </c>
       <c r="P13" t="n">
-        <v>0</v>
+        <v>1.98</v>
       </c>
       <c r="Q13" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="R13" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S13" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T13" t="n">
-        <v>0</v>
+        <v>3.19</v>
       </c>
       <c r="U13" t="n">
-        <v>0</v>
+        <v>1.32</v>
       </c>
       <c r="V13" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X13" t="n">
-        <v>0</v>
+        <v>2.88</v>
       </c>
       <c r="Y13" t="n">
-        <v>0</v>
+        <v>2.15</v>
       </c>
       <c r="Z13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA13" t="n">
-        <v>0</v>
+        <v>3.9</v>
       </c>
       <c r="AB13" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="AC13" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD13" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
@@ -2155,10 +2155,10 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH13" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AI13" t="n">
         <v>0</v>

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -643,12 +643,12 @@
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>USM Alger</t>
+          <t>Ben Aknoun</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>MB Rouisset</t>
+          <t>CS Constantine</t>
         </is>
       </c>
       <c r="G2" t="n">
@@ -772,12 +772,12 @@
       </c>
       <c r="E3" t="inlineStr">
         <is>
-          <t>Ben Aknoun</t>
+          <t>USM Alger</t>
         </is>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>CS Constantine</t>
+          <t>MB Rouisset</t>
         </is>
       </c>
       <c r="G3" t="n">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>CR Belouizdad</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ES Sétif</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>CR Belouizdad</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ES Sétif</t>
         </is>
       </c>
       <c r="G9" t="n">

--- a/jogos_2025-10-09.xlsx
+++ b/jogos_2025-10-09.xlsx
@@ -757,7 +757,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>12:00</t>
+          <t>13:00</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -877,7 +877,7 @@
         <v>0</v>
       </c>
       <c r="AK3" s="3" t="n">
-        <v>45939.5</v>
+        <v>45939.54166666666</v>
       </c>
     </row>
     <row r="4">
@@ -901,12 +901,12 @@
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>MC Alger</t>
+          <t>Oued Akbou</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Paradou AC</t>
+          <t>El Bayadh</t>
         </is>
       </c>
       <c r="G4" t="n">
@@ -1030,12 +1030,12 @@
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>JS Kabylie</t>
+          <t>ES Mostaganem</t>
         </is>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>USM Khenchela</t>
+          <t>ASO Chlef</t>
         </is>
       </c>
       <c r="G5" t="n">
@@ -1159,12 +1159,12 @@
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>MC Oran</t>
+          <t>JS Kabylie</t>
         </is>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>JS Saoura</t>
+          <t>USM Khenchela</t>
         </is>
       </c>
       <c r="G6" t="n">
@@ -1288,12 +1288,12 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Oued Akbou</t>
+          <t>MC Oran</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>El Bayadh</t>
+          <t>JS Saoura</t>
         </is>
       </c>
       <c r="G7" t="n">
@@ -1417,12 +1417,12 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>ES Mostaganem</t>
+          <t>MC Alger</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>ASO Chlef</t>
+          <t>Paradou AC</t>
         </is>
       </c>
       <c r="G8" t="n">
@@ -1687,7 +1687,7 @@
         <v>0</v>
       </c>
       <c r="H10" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>0</v>
@@ -1697,65 +1697,65 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>incomplete</t>
+          <t>complete</t>
         </is>
       </c>
       <c r="L10" t="n">
-        <v>2.4</v>
+        <v>2.15</v>
       </c>
       <c r="M10" t="n">
-        <v>3.25</v>
+        <v>3.23</v>
       </c>
       <c r="N10" t="n">
-        <v>2.85</v>
+        <v>3.1</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>2.87</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>3.45</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S10" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="T10" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U10" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V10" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X10" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="Y10" t="n">
-        <v>2.05</v>
+        <v>2.29</v>
       </c>
       <c r="Z10" t="n">
-        <v>1.68</v>
+        <v>1.6</v>
       </c>
       <c r="AA10" t="n">
-        <v>0</v>
+        <v>3.88</v>
       </c>
       <c r="AB10" t="n">
-        <v>0</v>
+        <v>1.2</v>
       </c>
       <c r="AC10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AD10" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
@@ -1764,20 +1764,20 @@
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['71']</t>
         </is>
       </c>
       <c r="AG10" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="AH10" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AI10" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AJ10" t="n">
-        <v>0</v>
+        <v>2.2</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45939.79166666666</v>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.75</v>
+        <v>1.83</v>
       </c>
       <c r="M11" t="n">
-        <v>3.45</v>
+        <v>3.26</v>
       </c>
       <c r="N11" t="n">
-        <v>4.5</v>
+        <v>4.33</v>
       </c>
       <c r="O11" t="n">
-        <v>0</v>
+        <v>2.51</v>
       </c>
       <c r="P11" t="n">
-        <v>0</v>
+        <v>1.92</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>4.8</v>
       </c>
       <c r="R11" t="n">
-        <v>0</v>
+        <v>1.59</v>
       </c>
       <c r="S11" t="n">
-        <v>0</v>
+        <v>2.4</v>
       </c>
       <c r="T11" t="n">
-        <v>0</v>
+        <v>3.5</v>
       </c>
       <c r="U11" t="n">
-        <v>0</v>
+        <v>1.25</v>
       </c>
       <c r="V11" t="n">
-        <v>0</v>
+        <v>1.04</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.56</v>
       </c>
       <c r="X11" t="n">
-        <v>0</v>
+        <v>2.41</v>
       </c>
       <c r="Y11" t="n">
-        <v>2.1</v>
+        <v>2.56</v>
       </c>
       <c r="Z11" t="n">
+        <v>1.48</v>
+      </c>
+      <c r="AA11" t="n">
+        <v>5</v>
+      </c>
+      <c r="AB11" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="AC11" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AD11" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AE11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF11" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG11" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AH11" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AI11" t="n">
         <v>1.65</v>
       </c>
-      <c r="AA11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AB11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AC11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AD11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF11" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AH11" t="n">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ11" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45939.8125</v>
@@ -1923,7 +1923,7 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>Canada Canadian Premier League</t>
+          <t>Chile Primera División</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
@@ -1933,12 +1933,12 @@
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>York9 FC</t>
+          <t>Universidad Católica</t>
         </is>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Pacific FC</t>
+          <t>Ñublense</t>
         </is>
       </c>
       <c r="G12" t="n">
@@ -1959,61 +1959,61 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.85</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>3.25</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>2.47</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>2.05</v>
       </c>
       <c r="Q12" t="n">
-        <v>0</v>
+        <v>4.4</v>
       </c>
       <c r="R12" t="n">
-        <v>0</v>
+        <v>1.4</v>
       </c>
       <c r="S12" t="n">
-        <v>0</v>
+        <v>2.65</v>
       </c>
       <c r="T12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="V12" t="n">
-        <v>0</v>
+        <v>1.06</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>1.36</v>
       </c>
       <c r="X12" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="Y12" t="n">
-        <v>0</v>
+        <v>2.1</v>
       </c>
       <c r="Z12" t="n">
-        <v>0</v>
+        <v>1.7</v>
       </c>
       <c r="AA12" t="n">
-        <v>0</v>
+        <v>3.7</v>
       </c>
       <c r="AB12" t="n">
-        <v>0</v>
+        <v>1.26</v>
       </c>
       <c r="AC12" t="n">
-        <v>0</v>
+        <v>1.83</v>
       </c>
       <c r="AD12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>0</v>
+        <v>1.34</v>
       </c>
       <c r="AH12" t="n">
-        <v>0</v>
+        <v>1.9</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.38</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45939.85416666666</v>
@@ -2052,7 +2052,7 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>Chile Primera División</t>
+          <t>Canada Canadian Premier League</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
@@ -2062,12 +2062,12 @@
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>Universidad Católica</t>
+          <t>York9 FC</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ñublense</t>
+          <t>Pacific FC</t>
         </is>
       </c>
       <c r="G13" t="n">
@@ -2084,87 +2084,87 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>suspended</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2</v>
+        <v>1.46</v>
       </c>
       <c r="M13" t="n">
-        <v>3.15</v>
+        <v>4</v>
       </c>
       <c r="N13" t="n">
-        <v>3.65</v>
+        <v>5.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.7</v>
+        <v>1.95</v>
       </c>
       <c r="P13" t="n">
-        <v>1.98</v>
+        <v>2.21</v>
       </c>
       <c r="Q13" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="R13" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="S13" t="n">
+        <v>2.94</v>
+      </c>
+      <c r="T13" t="n">
+        <v>2.49</v>
+      </c>
+      <c r="U13" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="V13" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W13" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="X13" t="n">
+        <v>3.78</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="Z13" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA13" t="n">
+        <v>2.57</v>
+      </c>
+      <c r="AB13" t="n">
+        <v>1.46</v>
+      </c>
+      <c r="AC13" t="n">
+        <v>1.89</v>
+      </c>
+      <c r="AD13" t="n">
+        <v>1.86</v>
+      </c>
+      <c r="AE13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF13" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AG13" t="n">
+        <v>1.16</v>
+      </c>
+      <c r="AH13" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AI13" t="n">
         <v>1.4</v>
       </c>
-      <c r="S13" t="n">
-        <v>2.6</v>
-      </c>
-      <c r="T13" t="n">
-        <v>3.19</v>
-      </c>
-      <c r="U13" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="V13" t="n">
-        <v>1.07</v>
-      </c>
-      <c r="W13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="X13" t="n">
-        <v>2.88</v>
-      </c>
-      <c r="Y13" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Z13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AA13" t="n">
-        <v>3.9</v>
-      </c>
-      <c r="AB13" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="AC13" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AD13" t="n">
-        <v>1.9</v>
-      </c>
-      <c r="AE13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AF13" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG13" t="n">
-        <v>1.36</v>
-      </c>
-      <c r="AH13" t="n">
-        <v>1.7</v>
-      </c>
-      <c r="AI13" t="n">
-        <v>0</v>
-      </c>
       <c r="AJ13" t="n">
-        <v>0</v>
+        <v>3.1</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45939.85416666666</v>
@@ -2217,61 +2217,61 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>3.2</v>
+        <v>3.52</v>
       </c>
       <c r="M14" t="n">
-        <v>3.25</v>
+        <v>2.95</v>
       </c>
       <c r="N14" t="n">
         <v>2.15</v>
       </c>
       <c r="O14" t="n">
-        <v>0</v>
+        <v>3.95</v>
       </c>
       <c r="P14" t="n">
-        <v>0</v>
+        <v>1.94</v>
       </c>
       <c r="Q14" t="n">
-        <v>0</v>
+        <v>2.67</v>
       </c>
       <c r="R14" t="n">
-        <v>0</v>
+        <v>1.44</v>
       </c>
       <c r="S14" t="n">
-        <v>0</v>
+        <v>2.6</v>
       </c>
       <c r="T14" t="n">
-        <v>0</v>
+        <v>3.2</v>
       </c>
       <c r="U14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="V14" t="n">
-        <v>0</v>
+        <v>1.07</v>
       </c>
       <c r="W14" t="n">
-        <v>0</v>
+        <v>1.51</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>2.63</v>
       </c>
       <c r="Y14" t="n">
-        <v>2.12</v>
+        <v>2.45</v>
       </c>
       <c r="Z14" t="n">
-        <v>1.64</v>
+        <v>1.5</v>
       </c>
       <c r="AA14" t="n">
-        <v>0</v>
+        <v>5.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>0</v>
+        <v>1.15</v>
       </c>
       <c r="AC14" t="n">
-        <v>0</v>
+        <v>2.02</v>
       </c>
       <c r="AD14" t="n">
-        <v>0</v>
+        <v>1.67</v>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
@@ -2284,16 +2284,16 @@
         </is>
       </c>
       <c r="AG14" t="n">
-        <v>0</v>
+        <v>1.35</v>
       </c>
       <c r="AH14" t="n">
-        <v>0</v>
+        <v>1.3</v>
       </c>
       <c r="AI14" t="n">
-        <v>0</v>
+        <v>2.55</v>
       </c>
       <c r="AJ14" t="n">
-        <v>0</v>
+        <v>1.8</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45939.89930555555</v>
